--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.19762777719381</v>
+        <v>8.644614513793995</v>
       </c>
       <c r="D2" t="n">
-        <v>53.99159191892351</v>
+        <v>8.773633686825072</v>
       </c>
       <c r="E2" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F2" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.248158750468948</v>
+        <v>1.340325796951204</v>
       </c>
       <c r="D3" t="n">
-        <v>7.962799024766015</v>
+        <v>1.293954841524477</v>
       </c>
       <c r="E3" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F3" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.48806313455994</v>
+        <v>4.79181025936599</v>
       </c>
       <c r="D4" t="n">
-        <v>30.28191663159023</v>
+        <v>4.920811452633412</v>
       </c>
       <c r="E4" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F4" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.72032598218359</v>
+        <v>4.342052972104833</v>
       </c>
       <c r="D5" t="n">
-        <v>25.95695444911968</v>
+        <v>4.218005097981949</v>
       </c>
       <c r="E5" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F5" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.66421581166211</v>
+        <v>2.545435069395092</v>
       </c>
       <c r="D6" t="n">
-        <v>15.47786234209278</v>
+        <v>2.515152630590076</v>
       </c>
       <c r="E6" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F6" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.30920221217451</v>
+        <v>5.412745359478358</v>
       </c>
       <c r="D7" t="n">
-        <v>32.89008249515093</v>
+        <v>5.344638405462027</v>
       </c>
       <c r="E7" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F7" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.30324600803421</v>
+        <v>8.17427747630556</v>
       </c>
       <c r="D8" t="n">
-        <v>51.14765295478589</v>
+        <v>8.311493605152707</v>
       </c>
       <c r="E8" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F8" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>53.76205414538201</v>
+        <v>8.736333798624576</v>
       </c>
       <c r="D9" t="n">
-        <v>55.57288425230243</v>
+        <v>9.030593690999146</v>
       </c>
       <c r="E9" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F9" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>65.45639784136422</v>
+        <v>10.63666464922169</v>
       </c>
       <c r="D10" t="n">
-        <v>32.09011618294042</v>
+        <v>5.214643879727818</v>
       </c>
       <c r="E10" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F10" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.2002296258544</v>
+        <v>7.18253731420134</v>
       </c>
       <c r="D11" t="n">
-        <v>21.61777960526309</v>
+        <v>3.512889185855252</v>
       </c>
       <c r="E11" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F11" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>65.10039739791171</v>
+        <v>10.57881457716065</v>
       </c>
       <c r="D12" t="n">
-        <v>18.78200440164881</v>
+        <v>3.052075715267931</v>
       </c>
       <c r="E12" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F12" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>18.42928471064962</v>
+        <v>2.994758765480563</v>
       </c>
       <c r="D13" t="n">
-        <v>18.20028837376135</v>
+        <v>2.957546860736219</v>
       </c>
       <c r="E13" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F13" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>53.25949535597889</v>
+        <v>8.654667995346569</v>
       </c>
       <c r="D14" t="n">
-        <v>14.05563565585408</v>
+        <v>2.284040794076288</v>
       </c>
       <c r="E14" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F14" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8.595227704894741</v>
+        <v>1.396724502045396</v>
       </c>
       <c r="D15" t="n">
-        <v>8.463508035592806</v>
+        <v>1.375320055783831</v>
       </c>
       <c r="E15" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F15" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>17.20327697169696</v>
+        <v>2.795532507900756</v>
       </c>
       <c r="D16" t="n">
-        <v>18.8953871205393</v>
+        <v>3.070500407087636</v>
       </c>
       <c r="E16" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F16" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>38.90420663441096</v>
+        <v>6.321933578091781</v>
       </c>
       <c r="D17" t="n">
-        <v>25.33462407464207</v>
+        <v>4.116876412129336</v>
       </c>
       <c r="E17" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F17" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>7.056539280494314</v>
+        <v>1.146687633080326</v>
       </c>
       <c r="D18" t="n">
-        <v>6.78713714267606</v>
+        <v>1.10290978568486</v>
       </c>
       <c r="E18" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F18" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>15.76166418555066</v>
+        <v>2.561270430151983</v>
       </c>
       <c r="D19" t="n">
-        <v>13.91670505707652</v>
+        <v>2.261464571774934</v>
       </c>
       <c r="E19" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F19" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>18.76444196102784</v>
+        <v>3.049221818667024</v>
       </c>
       <c r="D20" t="n">
-        <v>18.74555827060837</v>
+        <v>3.04615321897386</v>
       </c>
       <c r="E20" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F20" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>29.98248976846838</v>
+        <v>4.872154587376112</v>
       </c>
       <c r="D21" t="n">
-        <v>28.17191812583329</v>
+        <v>4.57793669544791</v>
       </c>
       <c r="E21" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F21" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>36.90805434992488</v>
+        <v>5.997558831862793</v>
       </c>
       <c r="D22" t="n">
-        <v>35.08367870716116</v>
+        <v>5.701097789913688</v>
       </c>
       <c r="E22" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F22" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>38.38146822493855</v>
+        <v>6.236988586552515</v>
       </c>
       <c r="D23" t="n">
-        <v>38.41900166333404</v>
+        <v>6.243087770291782</v>
       </c>
       <c r="E23" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F23" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>56.56835048589421</v>
+        <v>9.192356953957809</v>
       </c>
       <c r="D24" t="n">
-        <v>54.81533112496327</v>
+        <v>8.907491307806533</v>
       </c>
       <c r="E24" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F24" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>52.39646487437417</v>
+        <v>8.514425542085803</v>
       </c>
       <c r="D25" t="n">
-        <v>51.29690618602289</v>
+        <v>8.335747255228721</v>
       </c>
       <c r="E25" t="n">
-        <v>18.12747433874545</v>
+        <v>2.945714580046136</v>
       </c>
       <c r="F25" t="n">
-        <v>15.30369760533259</v>
+        <v>2.486850860866546</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
